--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V374"/>
+  <dimension ref="A1:V380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6088,10 +6088,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="A58" t="n">
+        <v>1101</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6145,7 +6143,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N58" s="2" t="n">
+      <c r="N58" s="1" t="n">
         <v>39421</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -6190,10 +6188,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="A59" t="n">
+        <v>1101</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6247,7 +6243,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N59" s="2" t="n">
+      <c r="N59" s="1" t="n">
         <v>37572</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -6292,10 +6288,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
+      <c r="A60" t="n">
+        <v>1103</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6349,7 +6343,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N60" s="2" t="n">
+      <c r="N60" s="1" t="n">
         <v>45875</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -6394,10 +6388,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
+      <c r="A61" t="n">
+        <v>1103</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6451,7 +6443,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N61" s="2" t="n">
+      <c r="N61" s="1" t="n">
         <v>45875</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -6496,10 +6488,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A62" t="n">
+        <v>1106</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6551,7 +6541,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="N62" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -6596,10 +6586,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A63" t="n">
+        <v>1106</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6651,7 +6639,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N63" s="2" t="n">
+      <c r="N63" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -6696,10 +6684,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A64" t="n">
+        <v>1106</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6751,7 +6737,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="N64" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -6796,10 +6782,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A65" t="n">
+        <v>1106</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6851,7 +6835,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N65" s="2" t="n">
+      <c r="N65" s="1" t="n">
         <v>45953</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -6896,10 +6880,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A66" t="n">
+        <v>1106</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6951,7 +6933,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="N66" s="1" t="n">
         <v>45875</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -6996,10 +6978,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A67" t="n">
+        <v>1106</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -7051,7 +7031,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="N67" s="1" t="n">
         <v>45797</v>
       </c>
       <c r="O67" t="inlineStr">
@@ -7096,10 +7076,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>1109</t>
-        </is>
+      <c r="A68" t="n">
+        <v>1109</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7153,7 +7131,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="N68" s="1" t="n">
         <v>45937</v>
       </c>
       <c r="O68" t="inlineStr">
@@ -7198,10 +7176,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A69" t="n">
+        <v>1111</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -7253,7 +7229,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N69" s="2" t="n">
+      <c r="N69" s="1" t="n">
         <v>45897</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -7298,10 +7274,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A70" t="n">
+        <v>1111</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -7353,7 +7327,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N70" s="2" t="n">
+      <c r="N70" s="1" t="n">
         <v>45986</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -7398,10 +7372,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A71" t="n">
+        <v>1111</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -7453,7 +7425,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N71" s="2" t="n">
+      <c r="N71" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -7498,10 +7470,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A72" t="n">
+        <v>1111</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -7553,7 +7523,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N72" s="2" t="n">
+      <c r="N72" s="1" t="n">
         <v>44334</v>
       </c>
       <c r="O72" t="inlineStr">
@@ -7598,10 +7568,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A73" t="n">
+        <v>1111</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -7653,7 +7621,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N73" s="2" t="n">
+      <c r="N73" s="1" t="n">
         <v>44334</v>
       </c>
       <c r="O73" t="inlineStr">
@@ -7698,10 +7666,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A74" t="n">
+        <v>1111</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -7745,7 +7711,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N74" s="2" t="n">
+      <c r="N74" s="1" t="n">
         <v>42797</v>
       </c>
       <c r="O74" t="inlineStr">
@@ -7790,10 +7756,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A75" t="n">
+        <v>1111</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -7845,7 +7809,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N75" s="2" t="n">
+      <c r="N75" s="1" t="n">
         <v>44466</v>
       </c>
       <c r="O75" t="inlineStr">
@@ -7890,10 +7854,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A76" t="n">
+        <v>1111</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -7945,7 +7907,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N76" s="2" t="n">
+      <c r="N76" s="1" t="n">
         <v>44466</v>
       </c>
       <c r="O76" t="inlineStr">
@@ -7990,10 +7952,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A77" t="n">
+        <v>1111</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -8045,7 +8005,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N77" s="2" t="n">
+      <c r="N77" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="O77" t="inlineStr">
@@ -8090,10 +8050,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A78" t="n">
+        <v>1111</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -8145,7 +8103,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N78" s="2" t="n">
+      <c r="N78" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="O78" t="inlineStr">
@@ -8190,10 +8148,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A79" t="n">
+        <v>1111</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -8237,7 +8193,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N79" s="2" t="n">
+      <c r="N79" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="O79" t="inlineStr">
@@ -8282,10 +8238,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A80" t="n">
+        <v>1111</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -8337,7 +8291,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N80" s="2" t="n">
+      <c r="N80" s="1" t="n">
         <v>44454</v>
       </c>
       <c r="O80" t="inlineStr">
@@ -8382,10 +8336,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A81" t="n">
+        <v>1111</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -8437,7 +8389,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N81" s="2" t="n">
+      <c r="N81" s="1" t="n">
         <v>44952</v>
       </c>
       <c r="O81" t="inlineStr">
@@ -8482,10 +8434,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A82" t="n">
+        <v>1111</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -8537,7 +8487,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="N82" s="1" t="n">
         <v>44952</v>
       </c>
       <c r="O82" t="inlineStr">
@@ -8582,10 +8532,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
+      <c r="A83" t="n">
+        <v>1113</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -8637,7 +8585,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N83" s="2" t="n">
+      <c r="N83" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="O83" t="inlineStr">
@@ -8682,10 +8630,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
+      <c r="A84" t="n">
+        <v>1114</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -8729,7 +8675,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N84" s="2" t="n">
+      <c r="N84" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O84" t="inlineStr">
@@ -8774,10 +8720,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
+      <c r="A85" t="n">
+        <v>1115</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -8829,7 +8773,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N85" s="2" t="n">
+      <c r="N85" s="1" t="n">
         <v>45973</v>
       </c>
       <c r="O85" t="inlineStr">
@@ -8874,10 +8818,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
+      <c r="A86" t="n">
+        <v>1119</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -8929,7 +8871,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N86" s="2" t="n">
+      <c r="N86" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="O86" t="inlineStr">
@@ -8974,10 +8916,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
+      <c r="A87" t="n">
+        <v>1119</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -9029,7 +8969,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N87" s="2" t="n">
+      <c r="N87" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="O87" t="inlineStr">
@@ -9074,10 +9014,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
+      <c r="A88" t="n">
+        <v>1121</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -9129,7 +9067,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N88" s="2" t="n">
+      <c r="N88" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="O88" t="inlineStr">
@@ -9174,10 +9112,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="A89" t="n">
+        <v>1201</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -9229,7 +9165,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N89" s="2" t="n">
+      <c r="N89" s="1" t="n">
         <v>45840</v>
       </c>
       <c r="O89" t="inlineStr">
@@ -9274,10 +9210,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="A90" t="n">
+        <v>1201</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -9329,7 +9263,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N90" s="2" t="n">
+      <c r="N90" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O90" t="inlineStr">
@@ -9374,10 +9308,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="A91" t="n">
+        <v>1201</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -9429,7 +9361,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N91" s="2" t="n">
+      <c r="N91" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O91" t="inlineStr">
@@ -9474,10 +9406,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="A92" t="n">
+        <v>1202</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -9529,7 +9459,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N92" s="2" t="n">
+      <c r="N92" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O92" t="inlineStr">
@@ -9574,10 +9504,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="A93" t="n">
+        <v>1202</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -9629,7 +9557,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N93" s="2" t="n">
+      <c r="N93" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O93" t="inlineStr">
@@ -9674,10 +9602,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A94" t="n">
+        <v>1203</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -9721,7 +9647,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N94" s="2" t="n">
+      <c r="N94" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O94" t="inlineStr">
@@ -9766,10 +9692,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A95" t="n">
+        <v>1204</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -9821,7 +9745,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N95" s="2" t="n">
+      <c r="N95" s="1" t="n">
         <v>45890</v>
       </c>
       <c r="O95" t="inlineStr">
@@ -9866,10 +9790,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A96" t="n">
+        <v>1206</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -9913,7 +9835,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N96" s="2" t="n">
+      <c r="N96" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="O96" t="inlineStr">
@@ -9958,10 +9880,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A97" t="n">
+        <v>1206</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -10013,7 +9933,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N97" s="2" t="n">
+      <c r="N97" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="O97" t="inlineStr">
@@ -10058,10 +9978,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A98" t="n">
+        <v>1206</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -10113,7 +10031,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N98" s="2" t="n">
+      <c r="N98" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O98" t="inlineStr">
@@ -10158,10 +10076,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A99" t="n">
+        <v>1206</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -10213,7 +10129,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N99" s="2" t="n">
+      <c r="N99" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O99" t="inlineStr">
@@ -10258,10 +10174,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A100" t="n">
+        <v>1206</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -10313,7 +10227,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N100" s="2" t="n">
+      <c r="N100" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O100" t="inlineStr">
@@ -10358,10 +10272,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A101" t="n">
+        <v>1206</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -10413,7 +10325,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N101" s="2" t="n">
+      <c r="N101" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O101" t="inlineStr">
@@ -10458,10 +10370,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>1209</t>
-        </is>
+      <c r="A102" t="n">
+        <v>1209</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -10515,7 +10425,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N102" s="2" t="n">
+      <c r="N102" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="O102" t="inlineStr">
@@ -10560,10 +10470,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
+      <c r="A103" t="n">
+        <v>1212</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -10617,7 +10525,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N103" s="2" t="n">
+      <c r="N103" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O103" t="inlineStr">
@@ -10662,10 +10570,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A104" t="n">
+        <v>1213</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -10717,7 +10623,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N104" s="2" t="n">
+      <c r="N104" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="O104" t="inlineStr">
@@ -10762,10 +10668,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A105" t="n">
+        <v>1213</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -10817,7 +10721,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N105" s="2" t="n">
+      <c r="N105" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="O105" t="inlineStr">
@@ -10862,10 +10766,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A106" t="n">
+        <v>1213</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -10917,7 +10819,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N106" s="2" t="n">
+      <c r="N106" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="O106" t="inlineStr">
@@ -10962,10 +10864,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A107" t="n">
+        <v>1213</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -11017,7 +10917,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N107" s="2" t="n">
+      <c r="N107" s="1" t="n">
         <v>45852</v>
       </c>
       <c r="O107" t="inlineStr">
@@ -11062,10 +10962,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
+      <c r="A108" t="n">
+        <v>1214</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -11117,7 +11015,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N108" s="2" t="n">
+      <c r="N108" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O108" t="inlineStr">
@@ -11162,10 +11060,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
+      <c r="A109" t="n">
+        <v>1214</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -11217,7 +11113,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N109" s="2" t="n">
+      <c r="N109" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O109" t="inlineStr">
@@ -11262,10 +11158,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A110" t="n">
+        <v>1218</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -11319,7 +11213,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N110" s="2" t="n">
+      <c r="N110" s="1" t="n">
         <v>45840</v>
       </c>
       <c r="O110" t="inlineStr">
@@ -11364,10 +11258,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A111" t="n">
+        <v>1218</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -11419,7 +11311,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N111" s="2" t="n">
+      <c r="N111" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="O111" t="inlineStr">
@@ -11464,10 +11356,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
+      <c r="A112" t="n">
+        <v>1301</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -11511,7 +11401,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N112" s="2" t="n">
+      <c r="N112" s="1" t="n">
         <v>42991</v>
       </c>
       <c r="O112" t="inlineStr">
@@ -11556,10 +11446,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
+      <c r="A113" t="n">
+        <v>1301</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -11611,7 +11499,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N113" s="2" t="n">
+      <c r="N113" s="1" t="n">
         <v>45890</v>
       </c>
       <c r="O113" t="inlineStr">
@@ -11656,10 +11544,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A114" t="n">
+        <v>1701</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -11713,7 +11599,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N114" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="O114" t="inlineStr">
@@ -11758,10 +11644,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A115" t="n">
+        <v>1701</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -11813,7 +11697,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N115" s="2" t="n">
+      <c r="N115" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="O115" t="inlineStr">
@@ -11858,10 +11742,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="A116" t="n">
+        <v>1702</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -11915,7 +11797,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N116" s="2" t="n">
+      <c r="N116" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O116" t="inlineStr">
@@ -11960,10 +11842,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="A117" t="n">
+        <v>1702</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -12015,7 +11895,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N117" s="2" t="n">
+      <c r="N117" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O117" t="inlineStr">
@@ -12060,10 +11940,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="A118" t="n">
+        <v>1703</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -12115,7 +11993,7 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="N118" s="2" t="n">
+      <c r="N118" s="1" t="n">
         <v>46013</v>
       </c>
       <c r="O118" t="inlineStr">
@@ -12160,10 +12038,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A119" t="n">
+        <v>1704</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -12217,7 +12093,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N119" s="2" t="n">
+      <c r="N119" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O119" t="inlineStr">
@@ -12262,10 +12138,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A120" t="n">
+        <v>1705</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -12319,7 +12193,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N120" s="2" t="n">
+      <c r="N120" s="1" t="n">
         <v>45827</v>
       </c>
       <c r="O120" t="inlineStr">
@@ -12364,10 +12238,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A121" t="n">
+        <v>1705</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -12421,7 +12293,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N121" s="2" t="n">
+      <c r="N121" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O121" t="inlineStr">
@@ -12466,10 +12338,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A122" t="n">
+        <v>1709</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -12521,7 +12391,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N122" s="2" t="n">
+      <c r="N122" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="O122" t="inlineStr">
@@ -12566,10 +12436,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A123" t="n">
+        <v>1709</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -12621,7 +12489,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N123" s="2" t="n">
+      <c r="N123" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O123" t="inlineStr">
@@ -12666,10 +12534,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A124" t="n">
+        <v>1709</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -12713,7 +12579,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N124" s="2" t="n">
+      <c r="N124" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O124" t="inlineStr">
@@ -12758,10 +12624,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A125" t="n">
+        <v>1709</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -12805,7 +12669,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N125" s="2" t="n">
+      <c r="N125" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="O125" t="inlineStr">
@@ -12850,10 +12714,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A126" t="n">
+        <v>1709</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -12905,7 +12767,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N126" s="2" t="n">
+      <c r="N126" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="O126" t="inlineStr">
@@ -12950,10 +12812,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A127" t="n">
+        <v>1709</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -12997,7 +12857,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N127" s="2" t="n">
+      <c r="N127" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O127" t="inlineStr">
@@ -13042,10 +12902,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A128" t="n">
+        <v>1709</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -13089,7 +12947,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N128" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O128" t="inlineStr">
@@ -13134,10 +12992,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A129" t="n">
+        <v>1709</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -13181,7 +13037,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N129" s="2" t="n">
+      <c r="N129" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O129" t="inlineStr">
@@ -13226,10 +13082,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A130" t="n">
+        <v>1709</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -13281,7 +13135,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N130" s="2" t="n">
+      <c r="N130" s="1" t="n">
         <v>44482</v>
       </c>
       <c r="O130" t="inlineStr">
@@ -13326,10 +13180,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A131" t="n">
+        <v>1709</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -13381,7 +13233,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N131" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="O131" t="inlineStr">
@@ -13426,10 +13278,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A132" t="n">
+        <v>1709</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -13473,7 +13323,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N132" s="2" t="n">
+      <c r="N132" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O132" t="inlineStr">
@@ -13518,10 +13368,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A133" t="n">
+        <v>1709</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -13565,7 +13413,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N133" s="2" t="n">
+      <c r="N133" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O133" t="inlineStr">
@@ -13610,10 +13458,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A134" t="n">
+        <v>1709</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -13667,7 +13513,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N134" s="2" t="n">
+      <c r="N134" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="O134" t="inlineStr">
@@ -13712,10 +13558,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A135" t="n">
+        <v>1710</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -13769,7 +13613,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N135" s="2" t="n">
+      <c r="N135" s="1" t="n">
         <v>45796</v>
       </c>
       <c r="O135" t="inlineStr">
@@ -13814,10 +13658,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A136" t="n">
+        <v>1710</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -13871,7 +13713,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N136" s="2" t="n">
+      <c r="N136" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O136" t="inlineStr">
@@ -13916,10 +13758,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A137" t="n">
+        <v>1710</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -13973,7 +13813,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N137" s="2" t="n">
+      <c r="N137" s="1" t="n">
         <v>43326</v>
       </c>
       <c r="O137" t="inlineStr">
@@ -14018,10 +13858,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A138" t="n">
+        <v>1710</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -14073,7 +13911,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N138" s="2" t="n">
+      <c r="N138" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="O138" t="inlineStr">
@@ -14118,10 +13956,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A139" t="n">
+        <v>1710</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -14175,7 +14011,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N139" s="2" t="n">
+      <c r="N139" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="O139" t="inlineStr">
@@ -14220,10 +14056,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A140" t="n">
+        <v>1710</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -14277,7 +14111,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N140" s="2" t="n">
+      <c r="N140" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O140" t="inlineStr">
@@ -14322,10 +14156,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A141" t="n">
+        <v>1711</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -14379,7 +14211,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N141" s="2" t="n">
+      <c r="N141" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="O141" t="inlineStr">
@@ -14424,10 +14256,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A142" t="n">
+        <v>1711</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -14479,7 +14309,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N142" s="2" t="n">
+      <c r="N142" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O142" t="inlineStr">
@@ -14524,10 +14354,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A143" t="n">
+        <v>1711</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -14581,7 +14409,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N143" s="2" t="n">
+      <c r="N143" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="O143" t="inlineStr">
@@ -14626,10 +14454,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A144" t="n">
+        <v>1711</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -14683,7 +14509,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N144" s="2" t="n">
+      <c r="N144" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O144" t="inlineStr">
@@ -14728,10 +14554,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A145" t="n">
+        <v>1712</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -14785,7 +14609,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N145" s="2" t="n">
+      <c r="N145" s="1" t="n">
         <v>45883</v>
       </c>
       <c r="O145" t="inlineStr">
@@ -14830,10 +14654,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A146" t="n">
+        <v>1712</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -14887,7 +14709,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N146" s="2" t="n">
+      <c r="N146" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="O146" t="inlineStr">
@@ -14932,10 +14754,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A147" t="n">
+        <v>1712</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -14989,7 +14809,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N147" s="2" t="n">
+      <c r="N147" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="O147" t="inlineStr">
@@ -15034,10 +14854,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A148" t="n">
+        <v>1712</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -15089,7 +14907,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N148" s="2" t="n">
+      <c r="N148" s="1" t="n">
         <v>45796</v>
       </c>
       <c r="O148" t="inlineStr">
@@ -15134,10 +14952,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A149" t="n">
+        <v>1712</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -15191,7 +15007,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N149" s="2" t="n">
+      <c r="N149" s="1" t="n">
         <v>44557</v>
       </c>
       <c r="O149" t="inlineStr">
@@ -15236,10 +15052,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A150" t="n">
+        <v>1712</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -15291,7 +15105,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N150" s="2" t="n">
+      <c r="N150" s="1" t="n">
         <v>44557</v>
       </c>
       <c r="O150" t="inlineStr">
@@ -15336,10 +15150,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A151" t="n">
+        <v>1712</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -15393,7 +15205,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N151" s="2" t="n">
+      <c r="N151" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="O151" t="inlineStr">
@@ -15438,10 +15250,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A152" t="n">
+        <v>1712</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -15495,7 +15305,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N152" s="2" t="n">
+      <c r="N152" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="O152" t="inlineStr">
@@ -15540,10 +15350,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A153" t="n">
+        <v>1712</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -15595,7 +15403,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N153" s="2" t="n">
+      <c r="N153" s="1" t="n">
         <v>45883</v>
       </c>
       <c r="O153" t="inlineStr">
@@ -15640,10 +15448,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A154" t="n">
+        <v>1712</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -15697,7 +15503,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N154" s="2" t="n">
+      <c r="N154" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="O154" t="inlineStr">
@@ -15742,10 +15548,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A155" t="n">
+        <v>1712</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -15789,7 +15593,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N155" s="2" t="n">
+      <c r="N155" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O155" t="inlineStr">
@@ -15834,10 +15638,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A156" t="n">
+        <v>1714</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -15889,7 +15691,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N156" s="2" t="n">
+      <c r="N156" s="1" t="n">
         <v>45986</v>
       </c>
       <c r="O156" t="inlineStr">
@@ -15934,10 +15736,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A157" t="n">
+        <v>1714</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -15989,7 +15789,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N157" s="2" t="n">
+      <c r="N157" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="O157" t="inlineStr">
@@ -16034,10 +15834,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A158" t="n">
+        <v>1714</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -16089,7 +15887,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N158" s="2" t="n">
+      <c r="N158" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O158" t="inlineStr">
@@ -16134,10 +15932,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A159" t="n">
+        <v>1714</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -16189,7 +15985,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N159" s="2" t="n">
+      <c r="N159" s="1" t="n">
         <v>45860</v>
       </c>
       <c r="O159" t="inlineStr">
@@ -16234,10 +16030,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A160" t="n">
+        <v>1714</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -16291,7 +16085,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N160" s="2" t="n">
+      <c r="N160" s="1" t="n">
         <v>43495</v>
       </c>
       <c r="O160" t="inlineStr">
@@ -16336,10 +16130,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A161" t="n">
+        <v>1714</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -16393,7 +16185,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N161" s="2" t="n">
+      <c r="N161" s="1" t="n">
         <v>45860</v>
       </c>
       <c r="O161" t="inlineStr">
@@ -16438,10 +16230,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A162" t="n">
+        <v>1716</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -16485,7 +16275,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N162" s="2" t="n">
+      <c r="N162" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O162" t="inlineStr">
@@ -16530,10 +16320,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A163" t="n">
+        <v>1716</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -16577,7 +16365,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N163" s="2" t="n">
+      <c r="N163" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O163" t="inlineStr">
@@ -16622,10 +16410,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A164" t="n">
+        <v>1716</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -16677,7 +16463,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N164" s="2" t="n">
+      <c r="N164" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O164" t="inlineStr">
@@ -16722,10 +16508,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A165" t="n">
+        <v>1716</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -16769,7 +16553,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N165" s="2" t="n">
+      <c r="N165" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O165" t="inlineStr">
@@ -16814,10 +16598,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A166" t="n">
+        <v>1716</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -16869,7 +16651,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N166" s="2" t="n">
+      <c r="N166" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O166" t="inlineStr">
@@ -16914,10 +16696,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A167" t="n">
+        <v>1716</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -16969,7 +16749,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N167" s="2" t="n">
+      <c r="N167" s="1" t="n">
         <v>45826</v>
       </c>
       <c r="O167" t="inlineStr">
@@ -17014,10 +16794,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A168" t="n">
+        <v>1716</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -17071,7 +16849,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N168" s="2" t="n">
+      <c r="N168" s="1" t="n">
         <v>45826</v>
       </c>
       <c r="O168" t="inlineStr">
@@ -17116,10 +16894,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A169" t="n">
+        <v>1716</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -17163,7 +16939,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N169" s="2" t="n">
+      <c r="N169" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O169" t="inlineStr">
@@ -17208,10 +16984,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A170" t="n">
+        <v>1716</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -17255,7 +17029,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N170" s="2" t="n">
+      <c r="N170" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O170" t="inlineStr">
@@ -17300,10 +17074,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A171" t="n">
+        <v>1716</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -17355,7 +17127,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N171" s="2" t="n">
+      <c r="N171" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O171" t="inlineStr">
@@ -17400,10 +17172,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A172" t="n">
+        <v>1716</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -17455,7 +17225,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N172" s="2" t="n">
+      <c r="N172" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O172" t="inlineStr">
@@ -17500,10 +17270,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
+      <c r="A173" t="n">
+        <v>1717</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -17555,7 +17323,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N173" s="2" t="n">
+      <c r="N173" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O173" t="inlineStr">
@@ -17600,10 +17368,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
+      <c r="A174" t="n">
+        <v>1718</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -17655,7 +17421,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N174" s="2" t="n">
+      <c r="N174" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O174" t="inlineStr">
@@ -17700,10 +17466,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
+      <c r="A175" t="n">
+        <v>1718</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -17757,7 +17521,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N175" s="2" t="n">
+      <c r="N175" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="O175" t="inlineStr">
@@ -17802,10 +17566,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>1719</t>
-        </is>
+      <c r="A176" t="n">
+        <v>1719</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -17859,7 +17621,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N176" s="2" t="n">
+      <c r="N176" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O176" t="inlineStr">
@@ -17904,10 +17666,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A177" t="n">
+        <v>1722</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -17959,7 +17719,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N177" s="2" t="n">
+      <c r="N177" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="O177" t="inlineStr">
@@ -18004,10 +17764,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A178" t="n">
+        <v>1722</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -18059,7 +17817,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N178" s="2" t="n">
+      <c r="N178" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="O178" t="inlineStr">
@@ -18104,10 +17862,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A179" t="n">
+        <v>1722</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -18159,7 +17915,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N179" s="2" t="n">
+      <c r="N179" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="O179" t="inlineStr">
@@ -18204,10 +17960,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A180" t="n">
+        <v>1722</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -18259,7 +18013,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N180" s="2" t="n">
+      <c r="N180" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="O180" t="inlineStr">
@@ -18304,10 +18058,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A181" t="n">
+        <v>1722</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -18359,7 +18111,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N181" s="2" t="n">
+      <c r="N181" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O181" t="inlineStr">
@@ -18404,10 +18156,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
+      <c r="A182" t="n">
+        <v>1724</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -18461,7 +18211,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N182" s="2" t="n">
+      <c r="N182" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="O182" t="inlineStr">
@@ -18506,10 +18256,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
+      <c r="A183" t="n">
+        <v>1724</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -18563,7 +18311,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N183" s="2" t="n">
+      <c r="N183" s="1" t="n">
         <v>45558</v>
       </c>
       <c r="O183" t="inlineStr">
@@ -18608,10 +18356,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
+      <c r="A184" t="n">
+        <v>1726</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -18665,7 +18411,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N184" s="2" t="n">
+      <c r="N184" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="O184" t="inlineStr">
@@ -18710,10 +18456,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
+      <c r="A185" t="n">
+        <v>1726</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -18765,7 +18509,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N185" s="2" t="n">
+      <c r="N185" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O185" t="inlineStr">
@@ -18810,10 +18554,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
+      <c r="A186" t="n">
+        <v>1726</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -18867,7 +18609,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N186" s="2" t="n">
+      <c r="N186" s="1" t="n">
         <v>45853</v>
       </c>
       <c r="O186" t="inlineStr">
@@ -18912,10 +18654,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A187" t="n">
+        <v>1728</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -18959,7 +18699,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N187" s="2" t="n">
+      <c r="N187" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="O187" t="inlineStr">
@@ -19004,10 +18744,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A188" t="n">
+        <v>1728</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -19051,7 +18789,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N188" s="2" t="n">
+      <c r="N188" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O188" t="inlineStr">
@@ -19096,10 +18834,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A189" t="n">
+        <v>1728</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -19151,7 +18887,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N189" s="2" t="n">
+      <c r="N189" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O189" t="inlineStr">
@@ -19196,10 +18932,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A190" t="n">
+        <v>1728</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -19251,7 +18985,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N190" s="2" t="n">
+      <c r="N190" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O190" t="inlineStr">
@@ -19296,10 +19030,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A191" t="n">
+        <v>1728</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -19343,7 +19075,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N191" s="2" t="n">
+      <c r="N191" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O191" t="inlineStr">
@@ -19388,10 +19120,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A192" t="n">
+        <v>1729</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -19445,7 +19175,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N192" s="2" t="n">
+      <c r="N192" s="1" t="n">
         <v>45950</v>
       </c>
       <c r="O192" t="inlineStr">
@@ -19490,10 +19220,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A193" t="n">
+        <v>1729</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -19547,7 +19275,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N193" s="2" t="n">
+      <c r="N193" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O193" t="inlineStr">
@@ -19592,10 +19320,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A194" t="n">
+        <v>1729</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -19647,7 +19373,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N194" s="2" t="n">
+      <c r="N194" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="O194" t="inlineStr">
@@ -19692,10 +19418,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A195" t="n">
+        <v>1729</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -19749,7 +19473,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N195" s="2" t="n">
+      <c r="N195" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O195" t="inlineStr">
@@ -19794,10 +19518,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A196" t="n">
+        <v>1729</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -19851,7 +19573,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N196" s="2" t="n">
+      <c r="N196" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="O196" t="inlineStr">
@@ -19896,10 +19618,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A197" t="n">
+        <v>1732</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -19951,7 +19671,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N197" s="2" t="n">
+      <c r="N197" s="1" t="n">
         <v>45853</v>
       </c>
       <c r="O197" t="inlineStr">
@@ -19996,10 +19716,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A198" t="n">
+        <v>1732</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -20053,7 +19771,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N198" s="2" t="n">
+      <c r="N198" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="O198" t="inlineStr">
@@ -20098,10 +19816,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A199" t="n">
+        <v>1732</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -20155,7 +19871,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N199" s="2" t="n">
+      <c r="N199" s="1" t="n">
         <v>45875</v>
       </c>
       <c r="O199" t="inlineStr">
@@ -20200,10 +19916,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A200" t="n">
+        <v>1732</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -20255,7 +19969,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N200" s="2" t="n">
+      <c r="N200" s="1" t="n">
         <v>45853</v>
       </c>
       <c r="O200" t="inlineStr">
@@ -20300,10 +20014,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
+      <c r="A201" t="n">
+        <v>1734</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -20355,7 +20067,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N201" s="2" t="n">
+      <c r="N201" s="1" t="n">
         <v>45853</v>
       </c>
       <c r="O201" t="inlineStr">
@@ -20400,10 +20112,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="A202" t="n">
+        <v>1802</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -20455,7 +20165,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N202" s="2" t="n">
+      <c r="N202" s="1" t="n">
         <v>45756</v>
       </c>
       <c r="O202" t="inlineStr">
@@ -20500,10 +20210,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A203" t="n">
+        <v>1803</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -20557,7 +20265,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N203" s="2" t="n">
+      <c r="N203" s="1" t="n">
         <v>45614</v>
       </c>
       <c r="O203" t="inlineStr">
@@ -20602,10 +20310,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A204" t="n">
+        <v>1803</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -20659,7 +20365,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N204" s="2" t="n">
+      <c r="N204" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O204" t="inlineStr">
@@ -20704,10 +20410,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A205" t="n">
+        <v>1803</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -20761,7 +20465,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N205" s="2" t="n">
+      <c r="N205" s="1" t="n">
         <v>45519</v>
       </c>
       <c r="O205" t="inlineStr">
@@ -20806,10 +20510,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A206" t="n">
+        <v>1805</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -20861,7 +20563,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N206" s="2" t="n">
+      <c r="N206" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O206" t="inlineStr">
@@ -20906,10 +20608,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A207" t="n">
+        <v>1805</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -20961,7 +20661,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N207" s="2" t="n">
+      <c r="N207" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O207" t="inlineStr">
@@ -21006,10 +20706,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
+      <c r="A208" t="n">
+        <v>1806</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -21063,7 +20761,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N208" s="2" t="n">
+      <c r="N208" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="O208" t="inlineStr">
@@ -21108,10 +20806,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
+      <c r="A209" t="n">
+        <v>1806</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -21165,7 +20861,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N209" s="2" t="n">
+      <c r="N209" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O209" t="inlineStr">
@@ -21210,10 +20906,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>1811</t>
-        </is>
+      <c r="A210" t="n">
+        <v>1811</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -21267,7 +20961,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N210" s="2" t="n">
+      <c r="N210" s="1" t="n">
         <v>45937</v>
       </c>
       <c r="O210" t="inlineStr">
@@ -21312,10 +21006,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A211" t="n">
+        <v>1812</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -21367,7 +21059,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N211" s="2" t="n">
+      <c r="N211" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O211" t="inlineStr">
@@ -21412,10 +21104,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A212" t="n">
+        <v>1812</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -21469,7 +21159,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N212" s="2" t="n">
+      <c r="N212" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O212" t="inlineStr">
@@ -21514,10 +21204,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A213" t="n">
+        <v>1813</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -21571,7 +21259,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N213" s="2" t="n">
+      <c r="N213" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="O213" t="inlineStr">
@@ -21616,10 +21304,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A214" t="n">
+        <v>1813</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -21673,7 +21359,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N214" s="2" t="n">
+      <c r="N214" s="1" t="n">
         <v>44270</v>
       </c>
       <c r="O214" t="inlineStr">
@@ -21718,10 +21404,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A215" t="n">
+        <v>1813</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -21775,7 +21459,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N215" s="2" t="n">
+      <c r="N215" s="1" t="n">
         <v>44466</v>
       </c>
       <c r="O215" t="inlineStr">
@@ -21820,10 +21504,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A216" t="n">
+        <v>1813</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -21877,7 +21559,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N216" s="2" t="n">
+      <c r="N216" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="O216" t="inlineStr">
@@ -21922,10 +21604,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A217" t="n">
+        <v>1813</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -21977,7 +21657,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N217" s="2" t="n">
+      <c r="N217" s="1" t="n">
         <v>44980</v>
       </c>
       <c r="O217" t="inlineStr">
@@ -22022,10 +21702,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A218" t="n">
+        <v>1818</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -22079,7 +21757,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N218" s="2" t="n">
+      <c r="N218" s="1" t="n">
         <v>45848</v>
       </c>
       <c r="O218" t="inlineStr">
@@ -22124,10 +21802,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A219" t="n">
+        <v>1823</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -22171,7 +21847,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N219" s="2" t="n">
+      <c r="N219" s="1" t="n">
         <v>46035</v>
       </c>
       <c r="O219" t="inlineStr">
@@ -22216,10 +21892,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A220" t="n">
+        <v>1823</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -22273,7 +21947,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N220" s="2" t="n">
+      <c r="N220" s="1" t="n">
         <v>43704</v>
       </c>
       <c r="O220" t="inlineStr">
@@ -22318,10 +21992,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A221" t="n">
+        <v>1823</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -22373,7 +22045,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N221" s="2" t="n">
+      <c r="N221" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="O221" t="inlineStr">
@@ -22418,10 +22090,8 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A222" t="n">
+        <v>1826</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -22475,7 +22145,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N222" s="2" t="n">
+      <c r="N222" s="1" t="n">
         <v>45883</v>
       </c>
       <c r="O222" t="inlineStr">
@@ -22520,10 +22190,8 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A223" t="n">
+        <v>1826</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -22575,7 +22243,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N223" s="2" t="n">
+      <c r="N223" s="1" t="n">
         <v>45855</v>
       </c>
       <c r="O223" t="inlineStr">
@@ -22620,10 +22288,8 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
+      <c r="A224" t="n">
+        <v>1827</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -22677,7 +22343,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N224" s="2" t="n">
+      <c r="N224" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="O224" t="inlineStr">
@@ -22722,10 +22388,8 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A225" t="n">
+        <v>1828</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -22769,7 +22433,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N225" s="2" t="n">
+      <c r="N225" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O225" t="inlineStr">
@@ -22814,10 +22478,8 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A226" t="n">
+        <v>1828</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -22869,7 +22531,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N226" s="2" t="n">
+      <c r="N226" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O226" t="inlineStr">
@@ -22914,10 +22576,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A227" t="n">
+        <v>1828</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -22969,7 +22629,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N227" s="2" t="n">
+      <c r="N227" s="1" t="n">
         <v>46021</v>
       </c>
       <c r="O227" t="inlineStr">
@@ -23014,10 +22674,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A228" t="n">
+        <v>1828</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -23071,7 +22729,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N228" s="2" t="n">
+      <c r="N228" s="1" t="n">
         <v>45880</v>
       </c>
       <c r="O228" t="inlineStr">
@@ -23116,10 +22774,8 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A229" t="n">
+        <v>1828</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -23163,7 +22819,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N229" s="2" t="n">
+      <c r="N229" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="O229" t="inlineStr">
@@ -23208,10 +22864,8 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A230" t="n">
+        <v>1828</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -23265,7 +22919,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N230" s="2" t="n">
+      <c r="N230" s="1" t="n">
         <v>45516</v>
       </c>
       <c r="O230" t="inlineStr">
@@ -23310,10 +22964,8 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A231" t="n">
+        <v>1828</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -23365,7 +23017,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N231" s="2" t="n">
+      <c r="N231" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="O231" t="inlineStr">
@@ -23410,10 +23062,8 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="A232" t="n">
+        <v>1829</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -23467,7 +23117,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N232" s="2" t="n">
+      <c r="N232" s="1" t="n">
         <v>45860</v>
       </c>
       <c r="O232" t="inlineStr">
@@ -23512,10 +23162,8 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
+      <c r="A233" t="n">
+        <v>1831</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -23567,7 +23215,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N233" s="2" t="n">
+      <c r="N233" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O233" t="inlineStr">
@@ -23612,10 +23260,8 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
+      <c r="A234" t="n">
+        <v>1832</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -23667,7 +23313,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N234" s="2" t="n">
+      <c r="N234" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="O234" t="inlineStr">
@@ -23712,10 +23358,8 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
+      <c r="A235" t="n">
+        <v>1832</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -23767,7 +23411,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N235" s="2" t="n">
+      <c r="N235" s="1" t="n">
         <v>43629</v>
       </c>
       <c r="O235" t="inlineStr">
@@ -23812,10 +23456,8 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
+      <c r="A236" t="n">
+        <v>1832</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -23869,7 +23511,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N236" s="2" t="n">
+      <c r="N236" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O236" t="inlineStr">
@@ -23914,10 +23556,8 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A237" t="n">
+        <v>1833</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -23971,7 +23611,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N237" s="2" t="n">
+      <c r="N237" s="1" t="n">
         <v>44489</v>
       </c>
       <c r="O237" t="inlineStr">
@@ -24016,10 +23656,8 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A238" t="n">
+        <v>1833</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -24073,7 +23711,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N238" s="2" t="n">
+      <c r="N238" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O238" t="inlineStr">
@@ -24118,10 +23756,8 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A239" t="n">
+        <v>1833</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -24165,7 +23801,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N239" s="2" t="n">
+      <c r="N239" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O239" t="inlineStr">
@@ -24210,10 +23846,8 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A240" t="n">
+        <v>1833</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -24267,7 +23901,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N240" s="2" t="n">
+      <c r="N240" s="1" t="n">
         <v>44685</v>
       </c>
       <c r="O240" t="inlineStr">
@@ -24312,10 +23946,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A241" t="n">
+        <v>1833</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -24369,7 +24001,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N241" s="2" t="n">
+      <c r="N241" s="1" t="n">
         <v>44273</v>
       </c>
       <c r="O241" t="inlineStr">
@@ -24414,10 +24046,8 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A242" t="n">
+        <v>1833</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -24471,7 +24101,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N242" s="2" t="n">
+      <c r="N242" s="1" t="n">
         <v>44433</v>
       </c>
       <c r="O242" t="inlineStr">
@@ -24516,10 +24146,8 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A243" t="n">
+        <v>1833</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -24573,7 +24201,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N243" s="2" t="n">
+      <c r="N243" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O243" t="inlineStr">
@@ -24618,10 +24246,8 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A244" t="n">
+        <v>1833</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -24675,7 +24301,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N244" s="2" t="n">
+      <c r="N244" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O244" t="inlineStr">
@@ -24720,10 +24346,8 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A245" t="n">
+        <v>1833</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -24777,7 +24401,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N245" s="2" t="n">
+      <c r="N245" s="1" t="n">
         <v>43810</v>
       </c>
       <c r="O245" t="inlineStr">
@@ -24822,10 +24446,8 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A246" t="n">
+        <v>1833</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -24879,7 +24501,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N246" s="2" t="n">
+      <c r="N246" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="O246" t="inlineStr">
@@ -24924,10 +24546,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A247" t="n">
+        <v>1833</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -24981,7 +24601,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N247" s="2" t="n">
+      <c r="N247" s="1" t="n">
         <v>44370</v>
       </c>
       <c r="O247" t="inlineStr">
@@ -25026,10 +24646,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A248" t="n">
+        <v>1833</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -25083,7 +24701,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N248" s="2" t="n">
+      <c r="N248" s="1" t="n">
         <v>45957</v>
       </c>
       <c r="O248" t="inlineStr">
@@ -25128,10 +24746,8 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A249" t="n">
+        <v>1833</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -25185,7 +24801,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N249" s="2" t="n">
+      <c r="N249" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O249" t="inlineStr">
@@ -25230,10 +24846,8 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A250" t="n">
+        <v>1833</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -25287,7 +24901,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N250" s="2" t="n">
+      <c r="N250" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O250" t="inlineStr">
@@ -25332,10 +24946,8 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A251" t="n">
+        <v>2102</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -25387,7 +24999,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N251" s="2" t="n">
+      <c r="N251" s="1" t="n">
         <v>45841</v>
       </c>
       <c r="O251" t="inlineStr">
@@ -25432,10 +25044,8 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A252" t="n">
+        <v>2102</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -25487,7 +25097,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N252" s="2" t="n">
+      <c r="N252" s="1" t="n">
         <v>45897</v>
       </c>
       <c r="O252" t="inlineStr">
@@ -25532,10 +25142,8 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A253" t="n">
+        <v>2102</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -25579,7 +25187,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N253" s="2" t="n">
+      <c r="N253" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="O253" t="inlineStr">
@@ -25624,10 +25232,8 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A254" t="n">
+        <v>2102</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -25679,7 +25285,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N254" s="2" t="n">
+      <c r="N254" s="1" t="n">
         <v>45895</v>
       </c>
       <c r="O254" t="inlineStr">
@@ -25724,10 +25330,8 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A255" t="n">
+        <v>2102</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -25779,7 +25383,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N255" s="2" t="n">
+      <c r="N255" s="1" t="n">
         <v>45861</v>
       </c>
       <c r="O255" t="inlineStr">
@@ -25824,10 +25428,8 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A256" t="n">
+        <v>2106</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -25879,7 +25481,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N256" s="2" t="n">
+      <c r="N256" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O256" t="inlineStr">
@@ -25924,10 +25526,8 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A257" t="n">
+        <v>2106</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -25971,7 +25571,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N257" s="2" t="n">
+      <c r="N257" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O257" t="inlineStr">
@@ -26016,10 +25616,8 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A258" t="n">
+        <v>2106</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -26071,7 +25669,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N258" s="2" t="n">
+      <c r="N258" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O258" t="inlineStr">
@@ -26116,10 +25714,8 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>2207</t>
-        </is>
+      <c r="A259" t="n">
+        <v>2207</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -26173,7 +25769,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N259" s="2" t="n">
+      <c r="N259" s="1" t="n">
         <v>45855</v>
       </c>
       <c r="O259" t="inlineStr">
@@ -26218,10 +25814,8 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2207</t>
-        </is>
+      <c r="A260" t="n">
+        <v>2207</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -26275,7 +25869,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N260" s="2" t="n">
+      <c r="N260" s="1" t="n">
         <v>45855</v>
       </c>
       <c r="O260" t="inlineStr">
@@ -26320,10 +25914,8 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
+      <c r="A261" t="n">
+        <v>2209</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -26375,7 +25967,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N261" s="2" t="n">
+      <c r="N261" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O261" t="inlineStr">
@@ -26420,10 +26012,8 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="A262" t="n">
+        <v>2301</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -26475,7 +26065,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N262" s="2" t="n">
+      <c r="N262" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="O262" t="inlineStr">
@@ -26520,10 +26110,8 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="A263" t="n">
+        <v>2301</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -26575,7 +26163,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N263" s="2" t="n">
+      <c r="N263" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O263" t="inlineStr">
@@ -26620,10 +26208,8 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="A264" t="n">
+        <v>2301</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -26675,7 +26261,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N264" s="2" t="n">
+      <c r="N264" s="1" t="n">
         <v>45980</v>
       </c>
       <c r="O264" t="inlineStr">
@@ -26720,10 +26306,8 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A265" t="n">
+        <v>2302</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -26775,7 +26359,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N265" s="2" t="n">
+      <c r="N265" s="1" t="n">
         <v>45981</v>
       </c>
       <c r="O265" t="inlineStr">
@@ -26820,10 +26404,8 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A266" t="n">
+        <v>2302</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -26875,7 +26457,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N266" s="2" t="n">
+      <c r="N266" s="1" t="n">
         <v>45981</v>
       </c>
       <c r="O266" t="inlineStr">
@@ -26920,10 +26502,8 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
+      <c r="A267" t="n">
+        <v>2702</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -26975,7 +26555,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N267" s="2" t="n">
+      <c r="N267" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O267" t="inlineStr">
@@ -27020,10 +26600,8 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2709</t>
-        </is>
+      <c r="A268" t="n">
+        <v>2709</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -27077,7 +26655,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N268" s="2" t="n">
+      <c r="N268" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="O268" t="inlineStr">
@@ -27122,10 +26700,8 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>2711</t>
-        </is>
+      <c r="A269" t="n">
+        <v>2711</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -27179,7 +26755,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N269" s="2" t="n">
+      <c r="N269" s="1" t="n">
         <v>45615</v>
       </c>
       <c r="O269" t="inlineStr">
@@ -27224,10 +26800,8 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
+      <c r="A270" t="n">
+        <v>2712</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -27281,7 +26855,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N270" s="2" t="n">
+      <c r="N270" s="1" t="n">
         <v>45880</v>
       </c>
       <c r="O270" t="inlineStr">
@@ -27326,10 +26900,8 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
+      <c r="A271" t="n">
+        <v>2712</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -27383,7 +26955,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N271" s="2" t="n">
+      <c r="N271" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="O271" t="inlineStr">
@@ -27428,10 +27000,8 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
+      <c r="A272" t="n">
+        <v>2713</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -27485,7 +27055,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N272" s="2" t="n">
+      <c r="N272" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="O272" t="inlineStr">
@@ -27530,10 +27100,8 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
+      <c r="A273" t="n">
+        <v>2713</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -27587,7 +27155,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N273" s="2" t="n">
+      <c r="N273" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="O273" t="inlineStr">
@@ -27632,10 +27200,8 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
+      <c r="A274" t="n">
+        <v>2715</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -27687,7 +27253,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N274" s="2" t="n">
+      <c r="N274" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O274" t="inlineStr">
@@ -27732,10 +27298,8 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="A275" t="n">
+        <v>2719</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -27789,7 +27353,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N275" s="2" t="n">
+      <c r="N275" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O275" t="inlineStr">
@@ -27834,10 +27398,8 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="A276" t="n">
+        <v>2719</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -27889,7 +27451,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N276" s="2" t="n">
+      <c r="N276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O276" t="inlineStr">
@@ -27934,10 +27496,8 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2720</t>
-        </is>
+      <c r="A277" t="n">
+        <v>2720</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -27991,7 +27551,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N277" s="2" t="n">
+      <c r="N277" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O277" t="inlineStr">
@@ -28036,10 +27596,8 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2720</t>
-        </is>
+      <c r="A278" t="n">
+        <v>2720</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -28093,7 +27651,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N278" s="2" t="n">
+      <c r="N278" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O278" t="inlineStr">
@@ -28138,10 +27696,8 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A279" t="n">
+        <v>2725</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -28193,7 +27749,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N279" s="2" t="n">
+      <c r="N279" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O279" t="inlineStr">
@@ -28238,10 +27794,8 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A280" t="n">
+        <v>2725</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -28293,7 +27847,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N280" s="2" t="n">
+      <c r="N280" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O280" t="inlineStr">
@@ -28338,10 +27892,8 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
+      <c r="A281" t="n">
+        <v>2727</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -28393,7 +27945,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N281" s="2" t="n">
+      <c r="N281" s="1" t="n">
         <v>45743</v>
       </c>
       <c r="O281" t="inlineStr">
@@ -28438,10 +27990,8 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
+      <c r="A282" t="n">
+        <v>2727</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -28493,7 +28043,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N282" s="2" t="n">
+      <c r="N282" s="1" t="n">
         <v>45602</v>
       </c>
       <c r="O282" t="inlineStr">
@@ -28538,10 +28088,8 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
+      <c r="A283" t="n">
+        <v>2727</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -28593,7 +28141,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N283" s="2" t="n">
+      <c r="N283" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="O283" t="inlineStr">
@@ -28638,10 +28186,8 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
+      <c r="A284" t="n">
+        <v>2732</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -28695,7 +28241,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N284" s="2" t="n">
+      <c r="N284" s="1" t="n">
         <v>45840</v>
       </c>
       <c r="O284" t="inlineStr">
@@ -28740,10 +28286,8 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
+      <c r="A285" t="n">
+        <v>2738</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -28787,7 +28331,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N285" s="2" t="n">
+      <c r="N285" s="1" t="n">
         <v>44473</v>
       </c>
       <c r="O285" t="inlineStr">
@@ -28832,10 +28376,8 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
+      <c r="A286" t="n">
+        <v>2743</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -28889,7 +28431,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N286" s="2" t="n">
+      <c r="N286" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O286" t="inlineStr">
@@ -28934,10 +28476,8 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
+      <c r="A287" t="n">
+        <v>2744</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -28991,7 +28531,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N287" s="2" t="n">
+      <c r="N287" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="O287" t="inlineStr">
@@ -29036,10 +28576,8 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
+      <c r="A288" t="n">
+        <v>2744</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -29083,7 +28621,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N288" s="2" t="n">
+      <c r="N288" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="O288" t="inlineStr">
@@ -29128,10 +28666,8 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A289" t="n">
+        <v>2805</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -29175,7 +28711,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N289" s="2" t="n">
+      <c r="N289" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O289" t="inlineStr">
@@ -29220,10 +28756,8 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A290" t="n">
+        <v>2805</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -29267,7 +28801,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N290" s="2" t="n">
+      <c r="N290" s="1" t="n">
         <v>46085</v>
       </c>
       <c r="O290" t="inlineStr">
@@ -29312,10 +28846,8 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A291" t="n">
+        <v>2805</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -29367,7 +28899,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N291" s="2" t="n">
+      <c r="N291" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="O291" t="inlineStr">
@@ -29412,10 +28944,8 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A292" t="n">
+        <v>2805</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -29459,7 +28989,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N292" s="2" t="n">
+      <c r="N292" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O292" t="inlineStr">
@@ -29504,10 +29034,8 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+      <c r="A293" t="n">
+        <v>2810</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -29551,7 +29079,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N293" s="2" t="n">
+      <c r="N293" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="O293" t="inlineStr">
@@ -29596,10 +29124,8 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+      <c r="A294" t="n">
+        <v>2810</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -29653,7 +29179,7 @@
           <t>Bimensual</t>
         </is>
       </c>
-      <c r="N294" s="2" t="n">
+      <c r="N294" s="1" t="n">
         <v>44273</v>
       </c>
       <c r="O294" t="inlineStr">
@@ -29698,10 +29224,8 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A295" t="n">
+        <v>2823</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -29755,7 +29279,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N295" s="2" t="n">
+      <c r="N295" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="O295" t="inlineStr">
@@ -29800,10 +29324,8 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A296" t="n">
+        <v>2823</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -29857,7 +29379,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N296" s="2" t="n">
+      <c r="N296" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="O296" t="inlineStr">
@@ -29902,10 +29424,8 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A297" t="n">
+        <v>2829</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -29959,7 +29479,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N297" s="2" t="n">
+      <c r="N297" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="O297" t="inlineStr">
@@ -30004,10 +29524,8 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A298" t="n">
+        <v>2829</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -30059,7 +29577,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N298" s="2" t="n">
+      <c r="N298" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O298" t="inlineStr">
@@ -30104,10 +29622,8 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A299" t="n">
+        <v>2829</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -30159,7 +29675,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N299" s="2" t="n">
+      <c r="N299" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O299" t="inlineStr">
@@ -30204,10 +29720,8 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A300" t="n">
+        <v>2829</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -30251,7 +29765,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N300" s="2" t="n">
+      <c r="N300" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="O300" t="inlineStr">
@@ -30296,10 +29810,8 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A301" t="n">
+        <v>2830</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -30351,7 +29863,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N301" s="2" t="n">
+      <c r="N301" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O301" t="inlineStr">
@@ -30396,10 +29908,8 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A302" t="n">
+        <v>2830</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -30451,7 +29961,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N302" s="2" t="n">
+      <c r="N302" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O302" t="inlineStr">
@@ -30496,10 +30006,8 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A303" t="n">
+        <v>2830</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -30553,7 +30061,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N303" s="2" t="n">
+      <c r="N303" s="1" t="n">
         <v>45855</v>
       </c>
       <c r="O303" t="inlineStr">
@@ -30598,10 +30106,8 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A304" t="n">
+        <v>2830</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -30653,7 +30159,7 @@
           <t>Bimensual</t>
         </is>
       </c>
-      <c r="N304" s="2" t="n">
+      <c r="N304" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O304" t="inlineStr">
@@ -30698,10 +30204,8 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A305" t="n">
+        <v>2830</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -30753,7 +30257,7 @@
           <t>Bimensual</t>
         </is>
       </c>
-      <c r="N305" s="2" t="n">
+      <c r="N305" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O305" t="inlineStr">
@@ -30798,10 +30302,8 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A306" t="n">
+        <v>2830</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -30855,7 +30357,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N306" s="2" t="n">
+      <c r="N306" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="O306" t="inlineStr">
@@ -30900,10 +30402,8 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A307" t="n">
+        <v>2830</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -30957,7 +30457,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N307" s="2" t="n">
+      <c r="N307" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="O307" t="inlineStr">
@@ -31002,10 +30502,8 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A308" t="n">
+        <v>2833</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -31057,7 +30555,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N308" s="2" t="n">
+      <c r="N308" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O308" t="inlineStr">
@@ -31102,10 +30600,8 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A309" t="n">
+        <v>2833</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -31157,7 +30653,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N309" s="2" t="n">
+      <c r="N309" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O309" t="inlineStr">
@@ -31202,10 +30698,8 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A310" t="n">
+        <v>2833</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -31257,7 +30751,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N310" s="2" t="n">
+      <c r="N310" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O310" t="inlineStr">
@@ -31302,10 +30796,8 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A311" t="n">
+        <v>2834</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -31359,7 +30851,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N311" s="2" t="n">
+      <c r="N311" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="O311" t="inlineStr">
@@ -31404,10 +30896,8 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A312" t="n">
+        <v>2834</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -31461,7 +30951,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N312" s="2" t="n">
+      <c r="N312" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="O312" t="inlineStr">
@@ -31506,10 +30996,8 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
+      <c r="A313" t="n">
+        <v>2840</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -31563,7 +31051,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N313" s="2" t="n">
+      <c r="N313" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O313" t="inlineStr">
@@ -31608,10 +31096,8 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
+      <c r="A314" t="n">
+        <v>2840</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -31665,7 +31151,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N314" s="2" t="n">
+      <c r="N314" s="1" t="n">
         <v>45971</v>
       </c>
       <c r="O314" t="inlineStr">
@@ -31710,10 +31196,8 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
+      <c r="A315" t="n">
+        <v>2842</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -31765,7 +31249,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N315" s="2" t="n">
+      <c r="N315" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O315" t="inlineStr">
@@ -31810,10 +31294,8 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
+      <c r="A316" t="n">
+        <v>2847</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -31865,7 +31347,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N316" s="2" t="n">
+      <c r="N316" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="O316" t="inlineStr">
@@ -31910,10 +31392,8 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="A317" t="n">
+        <v>2850</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -31965,7 +31445,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N317" s="2" t="n">
+      <c r="N317" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="O317" t="inlineStr">
@@ -32010,10 +31490,8 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="A318" t="n">
+        <v>2850</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -32065,7 +31543,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N318" s="2" t="n">
+      <c r="N318" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O318" t="inlineStr">
@@ -32110,10 +31588,8 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>3107</t>
-        </is>
+      <c r="A319" t="n">
+        <v>3107</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -32165,7 +31641,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N319" s="2" t="n">
+      <c r="N319" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O319" t="inlineStr">
@@ -32210,10 +31686,8 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
+      <c r="A320" t="n">
+        <v>3115</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -32265,7 +31739,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N320" s="2" t="n">
+      <c r="N320" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="O320" t="inlineStr">
@@ -32310,10 +31784,8 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A321" t="n">
+        <v>3117</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -32367,7 +31839,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N321" s="2" t="n">
+      <c r="N321" s="1" t="n">
         <v>45847</v>
       </c>
       <c r="O321" t="inlineStr">
@@ -32412,10 +31884,8 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A322" t="n">
+        <v>3117</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -32469,7 +31939,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N322" s="2" t="n">
+      <c r="N322" s="1" t="n">
         <v>45847</v>
       </c>
       <c r="O322" t="inlineStr">
@@ -32514,10 +31984,8 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
+      <c r="A323" t="n">
+        <v>3204</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -32569,7 +32037,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N323" s="2" t="n">
+      <c r="N323" s="1" t="n">
         <v>45840</v>
       </c>
       <c r="O323" t="inlineStr">
@@ -32614,10 +32082,8 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A324" t="n">
+        <v>3302</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -32671,7 +32137,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N324" s="2" t="n">
+      <c r="N324" s="1" t="n">
         <v>45953</v>
       </c>
       <c r="O324" t="inlineStr">
@@ -32716,10 +32182,8 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A325" t="n">
+        <v>3302</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -32771,7 +32235,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N325" s="2" t="n">
+      <c r="N325" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O325" t="inlineStr">
@@ -32816,10 +32280,8 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
+      <c r="A326" t="n">
+        <v>3710</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -32873,7 +32335,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N326" s="2" t="n">
+      <c r="N326" s="1" t="n">
         <v>45826</v>
       </c>
       <c r="O326" t="inlineStr">
@@ -32918,10 +32380,8 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
+      <c r="A327" t="n">
+        <v>3710</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -32975,7 +32435,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N327" s="2" t="n">
+      <c r="N327" s="1" t="n">
         <v>45890</v>
       </c>
       <c r="O327" t="inlineStr">
@@ -33020,10 +32480,8 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
+      <c r="A328" t="n">
+        <v>3713</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -33075,7 +32533,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N328" s="2" t="n">
+      <c r="N328" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O328" t="inlineStr">
@@ -33120,10 +32578,8 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
+      <c r="A329" t="n">
+        <v>3713</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -33177,7 +32633,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N329" s="2" t="n">
+      <c r="N329" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O329" t="inlineStr">
@@ -33222,10 +32678,8 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
+      <c r="A330" t="n">
+        <v>3718</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -33279,7 +32733,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N330" s="2" t="n">
+      <c r="N330" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O330" t="inlineStr">
@@ -33324,10 +32778,8 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
+      <c r="A331" t="n">
+        <v>3718</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -33381,7 +32833,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N331" s="2" t="n">
+      <c r="N331" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O331" t="inlineStr">
@@ -33426,10 +32878,8 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
+      <c r="A332" t="n">
+        <v>4101</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -33481,7 +32931,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N332" s="2" t="n">
+      <c r="N332" s="1" t="n">
         <v>45936</v>
       </c>
       <c r="O332" t="inlineStr">
@@ -33526,10 +32976,8 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
+      <c r="A333" t="n">
+        <v>4108</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -33581,7 +33029,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N333" s="2" t="n">
+      <c r="N333" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="O333" t="inlineStr">
@@ -33626,10 +33074,8 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
+      <c r="A334" t="n">
+        <v>4726</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -33681,7 +33127,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N334" s="2" t="n">
+      <c r="N334" s="1" t="n">
         <v>45890</v>
       </c>
       <c r="O334" t="inlineStr">
@@ -33726,10 +33172,8 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A335" t="n">
+        <v>4813</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -33781,7 +33225,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N335" s="2" t="n">
+      <c r="N335" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="O335" t="inlineStr">
@@ -33826,10 +33270,8 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A336" t="n">
+        <v>4813</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -33881,7 +33323,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N336" s="2" t="n">
+      <c r="N336" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="O336" t="inlineStr">
@@ -33926,10 +33368,8 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A337" t="n">
+        <v>4817</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -33983,7 +33423,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N337" s="2" t="n">
+      <c r="N337" s="1" t="n">
         <v>45770</v>
       </c>
       <c r="O337" t="inlineStr">
@@ -34028,10 +33468,8 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A338" t="n">
+        <v>4817</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -34085,7 +33523,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N338" s="2" t="n">
+      <c r="N338" s="1" t="n">
         <v>45770</v>
       </c>
       <c r="O338" t="inlineStr">
@@ -34130,10 +33568,8 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
+      <c r="A339" t="n">
+        <v>5801</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -34187,7 +33623,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N339" s="2" t="n">
+      <c r="N339" s="1" t="n">
         <v>45888</v>
       </c>
       <c r="O339" t="inlineStr">
@@ -34232,10 +33668,8 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A340" t="n">
+        <v>9119</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -34287,7 +33721,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N340" s="2" t="n">
+      <c r="N340" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O340" t="inlineStr">
@@ -34332,10 +33766,8 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A341" t="n">
+        <v>9119</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -34387,7 +33819,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N341" s="2" t="n">
+      <c r="N341" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O341" t="inlineStr">
@@ -34432,10 +33864,8 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A342" t="n">
+        <v>9119</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -34487,7 +33917,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N342" s="2" t="n">
+      <c r="N342" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O342" t="inlineStr">
@@ -34532,10 +33962,8 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A343" t="n">
+        <v>9119</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -34589,7 +34017,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N343" s="2" t="n">
+      <c r="N343" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="O343" t="inlineStr">
@@ -34634,10 +34062,8 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A344" t="n">
+        <v>9119</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -34691,7 +34117,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N344" s="2" t="n">
+      <c r="N344" s="1" t="n">
         <v>45813</v>
       </c>
       <c r="O344" t="inlineStr">
@@ -34736,10 +34162,8 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A345" t="n">
+        <v>9119</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -34793,7 +34217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N345" s="2" t="n">
+      <c r="N345" s="1" t="n">
         <v>45813</v>
       </c>
       <c r="O345" t="inlineStr">
@@ -34838,10 +34262,8 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A346" t="n">
+        <v>9119</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -34895,7 +34317,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N346" s="2" t="n">
+      <c r="N346" s="1" t="n">
         <v>45813</v>
       </c>
       <c r="O346" t="inlineStr">
@@ -34940,10 +34362,8 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A347" t="n">
+        <v>9119</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -34997,7 +34417,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N347" s="2" t="n">
+      <c r="N347" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="O347" t="inlineStr">
@@ -35042,10 +34462,8 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A348" t="n">
+        <v>9119</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -35099,7 +34517,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N348" s="2" t="n">
+      <c r="N348" s="1" t="n">
         <v>45890</v>
       </c>
       <c r="O348" t="inlineStr">
@@ -35144,10 +34562,8 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A349" t="n">
+        <v>9119</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -35201,7 +34617,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N349" s="2" t="n">
+      <c r="N349" s="1" t="n">
         <v>45847</v>
       </c>
       <c r="O349" t="inlineStr">
@@ -35246,10 +34662,8 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A350" t="n">
+        <v>9119</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -35303,7 +34717,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N350" s="2" t="n">
+      <c r="N350" s="1" t="n">
         <v>45847</v>
       </c>
       <c r="O350" t="inlineStr">
@@ -35348,10 +34762,8 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A351" t="n">
+        <v>9119</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -35405,7 +34817,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N351" s="2" t="n">
+      <c r="N351" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="O351" t="inlineStr">
@@ -35450,10 +34862,8 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A352" t="n">
+        <v>9119</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -35507,7 +34917,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N352" s="2" t="n">
+      <c r="N352" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="O352" t="inlineStr">
@@ -35552,10 +34962,8 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>9129</t>
-        </is>
+      <c r="A353" t="n">
+        <v>9129</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -35609,7 +35017,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N353" s="2" t="n">
+      <c r="N353" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O353" t="inlineStr">
@@ -35654,10 +35062,8 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
+      <c r="A354" t="n">
+        <v>9131</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -35709,7 +35115,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N354" s="2" t="n">
+      <c r="N354" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O354" t="inlineStr">
@@ -35754,10 +35160,8 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
+      <c r="A355" t="n">
+        <v>9131</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -35809,7 +35213,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N355" s="2" t="n">
+      <c r="N355" s="1" t="n">
         <v>45783</v>
       </c>
       <c r="O355" t="inlineStr">
@@ -35854,10 +35258,8 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
+      <c r="A356" t="n">
+        <v>9131</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -35911,7 +35313,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N356" s="2" t="n">
+      <c r="N356" s="1" t="n">
         <v>45946</v>
       </c>
       <c r="O356" t="inlineStr">
@@ -35956,10 +35358,8 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
+      <c r="A357" t="n">
+        <v>9131</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -36011,7 +35411,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N357" s="2" t="n">
+      <c r="N357" s="1" t="n">
         <v>46021</v>
       </c>
       <c r="O357" t="inlineStr">
@@ -36056,10 +35456,8 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>9899</t>
-        </is>
+      <c r="A358" t="n">
+        <v>9899</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -36113,7 +35511,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N358" s="2" t="n">
+      <c r="N358" s="1" t="n">
         <v>43776</v>
       </c>
       <c r="O358" t="inlineStr">
@@ -36158,10 +35556,8 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>9899</t>
-        </is>
+      <c r="A359" t="n">
+        <v>9899</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -36215,7 +35611,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N359" s="2" t="n">
+      <c r="N359" s="1" t="n">
         <v>43776</v>
       </c>
       <c r="O359" t="inlineStr">
@@ -36260,10 +35656,8 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A360" t="n">
+        <v>9913</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -36317,7 +35711,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N360" s="2" t="n">
+      <c r="N360" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O360" t="inlineStr">
@@ -36362,10 +35756,8 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A361" t="n">
+        <v>9913</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -36417,7 +35809,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N361" s="2" t="n">
+      <c r="N361" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="O361" t="inlineStr">
@@ -36462,10 +35854,8 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
+      <c r="A362" t="n">
+        <v>9922</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -36519,7 +35909,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N362" s="2" t="n">
+      <c r="N362" s="1" t="n">
         <v>45889</v>
       </c>
       <c r="O362" t="inlineStr">
@@ -36564,10 +35954,8 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>9923</t>
-        </is>
+      <c r="A363" t="n">
+        <v>9923</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -36621,7 +36009,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N363" s="2" t="n">
+      <c r="N363" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O363" t="inlineStr">
@@ -36666,10 +36054,8 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>9923</t>
-        </is>
+      <c r="A364" t="n">
+        <v>9923</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -36723,7 +36109,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N364" s="2" t="n">
+      <c r="N364" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="O364" t="inlineStr">
@@ -36768,10 +36154,8 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>9925</t>
-        </is>
+      <c r="A365" t="n">
+        <v>9925</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -36825,7 +36209,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N365" s="2" t="n">
+      <c r="N365" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O365" t="inlineStr">
@@ -36870,10 +36254,8 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>9925</t>
-        </is>
+      <c r="A366" t="n">
+        <v>9925</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -36927,7 +36309,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N366" s="2" t="n">
+      <c r="N366" s="1" t="n">
         <v>45776</v>
       </c>
       <c r="O366" t="inlineStr">
@@ -36972,10 +36354,8 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>9925</t>
-        </is>
+      <c r="A367" t="n">
+        <v>9925</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -37029,7 +36409,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N367" s="2" t="n">
+      <c r="N367" s="1" t="n">
         <v>45847</v>
       </c>
       <c r="O367" t="inlineStr">
@@ -37074,10 +36454,8 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
+      <c r="A368" t="n">
+        <v>9926</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -37121,7 +36499,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N368" s="2" t="n">
+      <c r="N368" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O368" t="inlineStr">
@@ -37166,10 +36544,8 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
+      <c r="A369" t="n">
+        <v>9926</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -37221,7 +36597,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N369" s="2" t="n">
+      <c r="N369" s="1" t="n">
         <v>45971</v>
       </c>
       <c r="O369" t="inlineStr">
@@ -37266,10 +36642,8 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>9941</t>
-        </is>
+      <c r="A370" t="n">
+        <v>9941</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -37321,7 +36695,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N370" s="2" t="n">
+      <c r="N370" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O370" t="inlineStr">
@@ -37366,10 +36740,8 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>9941</t>
-        </is>
+      <c r="A371" t="n">
+        <v>9941</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -37421,7 +36793,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N371" s="2" t="n">
+      <c r="N371" s="1" t="n">
         <v>45883</v>
       </c>
       <c r="O371" t="inlineStr">
@@ -37466,10 +36838,8 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>9943</t>
-        </is>
+      <c r="A372" t="n">
+        <v>9943</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -37523,7 +36893,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N372" s="2" t="n">
+      <c r="N372" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="O372" t="inlineStr">
@@ -37568,10 +36938,8 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>9943</t>
-        </is>
+      <c r="A373" t="n">
+        <v>9943</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -37625,7 +36993,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N373" s="2" t="n">
+      <c r="N373" s="1" t="n">
         <v>45827</v>
       </c>
       <c r="O373" t="inlineStr">
@@ -37670,10 +37038,8 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>9943</t>
-        </is>
+      <c r="A374" t="n">
+        <v>9943</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -37727,7 +37093,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N374" s="2" t="n">
+      <c r="N374" s="1" t="n">
         <v>45853</v>
       </c>
       <c r="O374" t="inlineStr">
@@ -37768,6 +37134,598 @@
       <c r="V374" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>118573</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INFORMÁTICA BIOMÉDICA</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I375" t="n">
+        <v>44</v>
+      </c>
+      <c r="J375" t="n">
+        <v>3</v>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>118571</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROBATORIO</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I376" t="n">
+        <v>26</v>
+      </c>
+      <c r="J376" t="n">
+        <v>2</v>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>118565</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I377" t="n">
+        <v>90</v>
+      </c>
+      <c r="J377" t="n">
+        <v>3</v>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>118566</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN VIROLOGÍA</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I378" t="n">
+        <v>110</v>
+      </c>
+      <c r="J378" t="n">
+        <v>4</v>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EIA</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>118574</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Especialización en Pediatría</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I379" t="n">
+        <v>197</v>
+      </c>
+      <c r="J379" t="n">
+        <v>6</v>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EIA</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="n">
+        <v>118576</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INGENIERÍA BIOMÉDICA</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I380" t="n">
+        <v>60</v>
+      </c>
+      <c r="J380" t="n">
+        <v>4</v>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>Ingeniería biomédica y afines</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V632"/>
+  <dimension ref="A1:V635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60746,10 +60746,8 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A616" t="n">
+        <v>1110</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -60801,7 +60799,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N616" s="2" t="n">
+      <c r="N616" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O616" t="inlineStr">
@@ -60846,10 +60844,8 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
+      <c r="A617" t="n">
+        <v>1114</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -60901,7 +60897,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N617" s="2" t="n">
+      <c r="N617" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O617" t="inlineStr">
@@ -60946,10 +60942,8 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A618" t="n">
+        <v>1705</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -61001,7 +60995,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N618" s="2" t="n">
+      <c r="N618" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O618" t="inlineStr">
@@ -61046,10 +61040,8 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A619" t="n">
+        <v>1722</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -61101,7 +61093,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N619" s="2" t="n">
+      <c r="N619" s="1" t="n">
         <v>44264</v>
       </c>
       <c r="O619" t="inlineStr">
@@ -61146,10 +61138,8 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A620" t="n">
+        <v>1729</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -61201,7 +61191,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N620" s="2" t="n">
+      <c r="N620" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="O620" t="inlineStr">
@@ -61246,10 +61236,8 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A621" t="n">
+        <v>1812</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -61301,7 +61289,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N621" s="2" t="n">
+      <c r="N621" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O621" t="inlineStr">
@@ -61346,10 +61334,8 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A622" t="n">
+        <v>1812</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -61401,7 +61387,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N622" s="2" t="n">
+      <c r="N622" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O622" t="inlineStr">
@@ -61446,10 +61432,8 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A623" t="n">
+        <v>1818</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -61501,7 +61485,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N623" s="2" t="n">
+      <c r="N623" s="1" t="n">
         <v>45937</v>
       </c>
       <c r="O623" t="inlineStr">
@@ -61546,10 +61530,8 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
+      <c r="A624" t="n">
+        <v>1827</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -61601,7 +61583,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N624" s="2" t="n">
+      <c r="N624" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O624" t="inlineStr">
@@ -61646,10 +61628,8 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A625" t="n">
+        <v>2102</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -61701,7 +61681,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N625" s="2" t="n">
+      <c r="N625" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O625" t="inlineStr">
@@ -61746,10 +61726,8 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A626" t="n">
+        <v>2102</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -61801,7 +61779,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N626" s="2" t="n">
+      <c r="N626" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O626" t="inlineStr">
@@ -61846,10 +61824,8 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A627" t="n">
+        <v>2102</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -61901,7 +61877,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N627" s="2" t="n">
+      <c r="N627" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O627" t="inlineStr">
@@ -61946,10 +61922,8 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>2720</t>
-        </is>
+      <c r="A628" t="n">
+        <v>2720</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -62001,7 +61975,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N628" s="2" t="n">
+      <c r="N628" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O628" t="inlineStr">
@@ -62046,10 +62020,8 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A629" t="n">
+        <v>2813</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -62101,7 +62073,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N629" s="2" t="n">
+      <c r="N629" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O629" t="inlineStr">
@@ -62146,10 +62118,8 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A630" t="n">
+        <v>2825</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -62201,7 +62171,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N630" s="2" t="n">
+      <c r="N630" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O630" t="inlineStr">
@@ -62246,10 +62216,8 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A631" t="n">
+        <v>4813</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -62301,7 +62269,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N631" s="2" t="n">
+      <c r="N631" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O631" t="inlineStr">
@@ -62346,10 +62314,8 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
+      <c r="A632" t="n">
+        <v>9922</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -62401,7 +62367,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N632" s="2" t="n">
+      <c r="N632" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O632" t="inlineStr">
@@ -62442,6 +62408,306 @@
       <c r="V632" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="F633" t="n">
+        <v>119019</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA EN SALUD</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I633" t="n">
+        <v>28</v>
+      </c>
+      <c r="J633" t="n">
+        <v>2</v>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr"/>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N633" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q633" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>Optometría, otros programas de ciencias de la salud</t>
+        </is>
+      </c>
+      <c r="S633" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V633" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>119018</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I634" t="n">
+        <v>26</v>
+      </c>
+      <c r="J634" t="n">
+        <v>2</v>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr"/>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N634" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q634" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S634" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T634" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V634" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F635" t="n">
+        <v>119017</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN CAMBIO CLIMATICO Y SOSTENIBILIDAD AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I635" t="n">
+        <v>40</v>
+      </c>
+      <c r="J635" t="n">
+        <v>3</v>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr"/>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N635" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T635" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V635" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V635"/>
+  <dimension ref="A1:V719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62412,10 +62412,8 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="A633" t="n">
+        <v>1829</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -62467,7 +62465,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N633" s="2" t="n">
+      <c r="N633" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="O633" t="inlineStr">
@@ -62512,10 +62510,8 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="A634" t="n">
+        <v>1829</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -62567,7 +62563,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N634" s="2" t="n">
+      <c r="N634" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="O634" t="inlineStr">
@@ -62612,10 +62608,8 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A635" t="n">
+        <v>2805</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -62667,7 +62661,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N635" s="2" t="n">
+      <c r="N635" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O635" t="inlineStr">
@@ -62708,6 +62702,8302 @@
       <c r="V635" t="inlineStr">
         <is>
           <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE PEREIRA - UTP</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F636" t="n">
+        <v>119146</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN PARA LAS CIENCIAS DE LA SALUD</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I636" t="n">
+        <v>50</v>
+      </c>
+      <c r="J636" t="n">
+        <v>4</v>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr"/>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N636" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q636" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S636" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T636" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V636" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F637" t="n">
+        <v>119155</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I637" t="n">
+        <v>100</v>
+      </c>
+      <c r="J637" t="n">
+        <v>8</v>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N637" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V637" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F638" t="n">
+        <v>119162</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANÁLISIS DE DATOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I638" t="n">
+        <v>30</v>
+      </c>
+      <c r="J638" t="n">
+        <v>2</v>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N638" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q638" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V638" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F639" t="n">
+        <v>119156</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I639" t="n">
+        <v>50</v>
+      </c>
+      <c r="J639" t="n">
+        <v>6</v>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N639" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q639" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V639" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F640" t="n">
+        <v>119148</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>MAESTRÍA DE ADMINISTRACIÓN DE NEGOCIOS (MBA)</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I640" t="n">
+        <v>42</v>
+      </c>
+      <c r="J640" t="n">
+        <v>3</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N640" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q640" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V640" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F641" t="n">
+        <v>119143</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I641" t="n">
+        <v>42</v>
+      </c>
+      <c r="J641" t="n">
+        <v>3</v>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N641" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q641" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V641" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL ATLANTICO</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Puerto Colombia</t>
+        </is>
+      </c>
+      <c r="F642" t="n">
+        <v>119164</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN TEORÍA DEL DELITO Y CASACIÓN PENAL</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I642" t="n">
+        <v>26</v>
+      </c>
+      <c r="J642" t="n">
+        <v>2</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N642" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q642" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V642" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL ATLANTICO</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Puerto Colombia</t>
+        </is>
+      </c>
+      <c r="F643" t="n">
+        <v>119144</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I643" t="n">
+        <v>48</v>
+      </c>
+      <c r="J643" t="n">
+        <v>4</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr"/>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N643" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q643" t="inlineStr">
+        <is>
+          <t>Educación no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V643" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL QUINDIO</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F644" t="n">
+        <v>119133</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GINECOLOGÍA Y OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I644" t="n">
+        <v>180</v>
+      </c>
+      <c r="J644" t="n">
+        <v>3</v>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N644" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q644" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V644" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL QUINDIO</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr"/>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="n">
+        <v>119111</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I645" t="n">
+        <v>40</v>
+      </c>
+      <c r="J645" t="n">
+        <v>4</v>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr"/>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N645" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q645" t="inlineStr">
+        <is>
+          <t>Bibliotecología, información y archivología</t>
+        </is>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>Bibliotecología, otros de ciencias sociales y humanas</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V645" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Fusagasugá</t>
+        </is>
+      </c>
+      <c r="F646" t="n">
+        <v>119069</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTERVENCIÓN PSICOSOCIAL</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I646" t="n">
+        <v>20</v>
+      </c>
+      <c r="J646" t="n">
+        <v>2</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr"/>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N646" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q646" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V646" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SUCRE</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F647" t="n">
+        <v>119130</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISCAPACIDAD</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I647" t="n">
+        <v>28</v>
+      </c>
+      <c r="J647" t="n">
+        <v>2</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N647" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="Q647" t="inlineStr">
+        <is>
+          <t>Bienestar no clasificado en otra parte</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V647" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F648" t="n">
+        <v>119022</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I648" t="n">
+        <v>27</v>
+      </c>
+      <c r="J648" t="n">
+        <v>2</v>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="N648" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q648" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T648" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V648" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F649" t="n">
+        <v>119082</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MUSICOTERAPIA</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I649" t="n">
+        <v>48</v>
+      </c>
+      <c r="J649" t="n">
+        <v>4</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N649" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q649" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T649" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V649" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F650" t="n">
+        <v>119081</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MUSICOTERAPIA</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I650" t="n">
+        <v>48</v>
+      </c>
+      <c r="J650" t="n">
+        <v>4</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N650" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q650" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr"/>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="n">
+        <v>119113</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DEL TRABAJO Y GESTIÓN HUMANA</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I651" t="n">
+        <v>25</v>
+      </c>
+      <c r="J651" t="n">
+        <v>2</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N651" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q651" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F652" t="n">
+        <v>119132</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RADIOLOGÍA ORAL Y MAXILOFACIAL</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I652" t="n">
+        <v>42</v>
+      </c>
+      <c r="J652" t="n">
+        <v>4</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N652" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q652" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>Odontología</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F653" t="n">
+        <v>119168</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN SOSTENIBLE DEL AGUA</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I653" t="n">
+        <v>42</v>
+      </c>
+      <c r="J653" t="n">
+        <v>4</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N653" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q653" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V653" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F654" t="n">
+        <v>119089</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO LABORAL Y SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I654" t="n">
+        <v>28</v>
+      </c>
+      <c r="J654" t="n">
+        <v>2</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N654" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q654" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T654" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V654" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F655" t="n">
+        <v>119059</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y GESTIÓN DE SOLUCIONES DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I655" t="n">
+        <v>24</v>
+      </c>
+      <c r="J655" t="n">
+        <v>2</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N655" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q655" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T655" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V655" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F656" t="n">
+        <v>119136</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN TERAPIA MANUAL ORTOPÉDICA</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I656" t="n">
+        <v>27</v>
+      </c>
+      <c r="J656" t="n">
+        <v>2</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N656" s="2" t="n">
+        <v>45044</v>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q656" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T656" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V656" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F657" t="n">
+        <v>119166</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FORMACIÓN ÉTICA Y RELIGIOSA EN LA ERA DIGITAL</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I657" t="n">
+        <v>36</v>
+      </c>
+      <c r="J657" t="n">
+        <v>3</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N657" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q657" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T657" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V657" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F658" t="n">
+        <v>119151</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GENÉTICA MÉDICA</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I658" t="n">
+        <v>147</v>
+      </c>
+      <c r="J658" t="n">
+        <v>6</v>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N658" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q658" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T658" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V658" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr"/>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="n">
+        <v>119106</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO CONSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I659" t="n">
+        <v>25</v>
+      </c>
+      <c r="J659" t="n">
+        <v>2</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N659" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q659" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T659" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V659" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>1726</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE ORIENTE -UCO</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F660" t="n">
+        <v>119070</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN BIG DATA Y ANALÍTICA</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I660" t="n">
+        <v>22</v>
+      </c>
+      <c r="J660" t="n">
+        <v>2</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N660" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q660" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V660" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr"/>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="n">
+        <v>119110</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORIA Y GESTIÓN DE RIESGOS</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I661" t="n">
+        <v>25</v>
+      </c>
+      <c r="J661" t="n">
+        <v>2</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N661" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q661" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T661" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V661" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F662" t="n">
+        <v>119088</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DIDÁCTICA DE LAS LENGUAS EXTRANJERAS</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I662" t="n">
+        <v>40</v>
+      </c>
+      <c r="J662" t="n">
+        <v>3</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N662" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q662" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T662" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V662" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BOYACA UNIBOYACA</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F663" t="n">
+        <v>119060</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN INTEGRAL DEL RECURSO HÍDRICO</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I663" t="n">
+        <v>28</v>
+      </c>
+      <c r="J663" t="n">
+        <v>2</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N663" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q663" t="inlineStr">
+        <is>
+          <t>Ingeniería y procesos químicos</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V663" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MANUELA BELTRAN-UMB-</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F664" t="n">
+        <v>118900</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BIOESTADÍSTICA</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I664" t="n">
+        <v>53</v>
+      </c>
+      <c r="J664" t="n">
+        <v>4</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N664" s="2" t="n">
+        <v>45309</v>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q664" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V664" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MANUELA BELTRAN-UMB-</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F665" t="n">
+        <v>118899</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN TECNOLOGÍAS PARA EL MANEJO DE AGUAS Y RESIDUOS</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I665" t="n">
+        <v>53</v>
+      </c>
+      <c r="J665" t="n">
+        <v>4</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N665" s="2" t="n">
+        <v>45362</v>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q665" t="inlineStr">
+        <is>
+          <t>Tecnología de protección del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V665" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>1807</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F666" t="n">
+        <v>119165</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SALUD FAMILIAR Y COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I666" t="n">
+        <v>24</v>
+      </c>
+      <c r="J666" t="n">
+        <v>2</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N666" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q666" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>Optometría, otros programas de ciencias de la salud</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V666" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>1807</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F667" t="n">
+        <v>119167</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO DE FAMILIA</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I667" t="n">
+        <v>39</v>
+      </c>
+      <c r="J667" t="n">
+        <v>3</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N667" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V667" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="n">
+        <v>119114</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y GESTIÓN DE CIUDADES INCLUSIVAS</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I668" t="n">
+        <v>24</v>
+      </c>
+      <c r="J668" t="n">
+        <v>2</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N668" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>Arquitectura y urbanismo</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V668" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F669" t="n">
+        <v>119131</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I669" t="n">
+        <v>24</v>
+      </c>
+      <c r="J669" t="n">
+        <v>1</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N669" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V669" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F670" t="n">
+        <v>118958</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN NEGOCIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I670" t="n">
+        <v>40</v>
+      </c>
+      <c r="J670" t="n">
+        <v>4</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N670" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F671" t="n">
+        <v>119139</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN HIDROGEOLOGIA</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I671" t="n">
+        <v>25</v>
+      </c>
+      <c r="J671" t="n">
+        <v>4</v>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N671" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F672" t="n">
+        <v>119033</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EXTENSIÓN E INNOVACIÓN RURAL</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I672" t="n">
+        <v>22</v>
+      </c>
+      <c r="J672" t="n">
+        <v>2</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N672" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V672" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>UNIDAD CENTRAL DEL VALLE DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="F673" t="n">
+        <v>119147</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BILINGÜÍSMO Y EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I673" t="n">
+        <v>40</v>
+      </c>
+      <c r="J673" t="n">
+        <v>4</v>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N673" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V673" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATÓLICA LUIS AMIGÓ</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F674" t="n">
+        <v>119030</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN FINANZAS</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I674" t="n">
+        <v>25</v>
+      </c>
+      <c r="J674" t="n">
+        <v>2</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N674" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V674" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F675" t="n">
+        <v>119071</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN NEUROPSICOLOGÍA ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I675" t="n">
+        <v>25</v>
+      </c>
+      <c r="J675" t="n">
+        <v>2</v>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N675" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V675" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="F676" t="n">
+        <v>119039</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FENÓMENO RELIGIOSO, ÉTICA Y PAZ</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I676" t="n">
+        <v>26</v>
+      </c>
+      <c r="J676" t="n">
+        <v>2</v>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr"/>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N676" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V676" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="n">
+        <v>119112</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTELIGENCIA DE NEGOCIOS PARA LA TOMA DE DECISIONES</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I677" t="n">
+        <v>24</v>
+      </c>
+      <c r="J677" t="n">
+        <v>2</v>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr"/>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N677" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V677" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F678" t="n">
+        <v>119066</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE LA BIOECONOMÍA Y GOBERNANZA BIOTECNOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I678" t="n">
+        <v>43</v>
+      </c>
+      <c r="J678" t="n">
+        <v>3</v>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr"/>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N678" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V678" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F679" t="n">
+        <v>119065</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE LA BIOECONOMÍA Y GOBERNANZA BIOTECNOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I679" t="n">
+        <v>43</v>
+      </c>
+      <c r="J679" t="n">
+        <v>3</v>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr"/>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N679" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q679" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V679" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F680" t="n">
+        <v>119038</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FAMILIAS Y CONSTRUCCIÓN DE PAZ</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I680" t="n">
+        <v>51</v>
+      </c>
+      <c r="J680" t="n">
+        <v>4</v>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr"/>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N680" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V680" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F681" t="n">
+        <v>119037</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FAMILIAS Y CONSTRUCCIÓN DE PAZ</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I681" t="n">
+        <v>51</v>
+      </c>
+      <c r="J681" t="n">
+        <v>4</v>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr"/>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N681" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q681" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V681" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F682" t="n">
+        <v>119078</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO Y DE LA GESTIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I682" t="n">
+        <v>29</v>
+      </c>
+      <c r="J682" t="n">
+        <v>2</v>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr"/>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N682" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V682" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F683" t="n">
+        <v>119061</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I683" t="n">
+        <v>28</v>
+      </c>
+      <c r="J683" t="n">
+        <v>2</v>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr"/>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N683" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V683" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F684" t="n">
+        <v>119062</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORIA EN SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I684" t="n">
+        <v>32</v>
+      </c>
+      <c r="J684" t="n">
+        <v>2</v>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr"/>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N684" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V684" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F685" t="n">
+        <v>119067</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN AMBIENTES DE APRENDIZAJE</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I685" t="n">
+        <v>44</v>
+      </c>
+      <c r="J685" t="n">
+        <v>4</v>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr"/>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N685" s="2" t="n">
+        <v>43812</v>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q685" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U685" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V685" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F686" t="n">
+        <v>119036</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN DE ENFERMERÍA EN CUIDADO CRITICO PARA EL ADULTO</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I686" t="n">
+        <v>26</v>
+      </c>
+      <c r="J686" t="n">
+        <v>2</v>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr"/>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N686" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V686" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>119072</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA Y CONTROL</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I687" t="n">
+        <v>26</v>
+      </c>
+      <c r="J687" t="n">
+        <v>2</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr"/>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N687" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V687" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F688" t="n">
+        <v>119073</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA Y CONTROL</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I688" t="n">
+        <v>26</v>
+      </c>
+      <c r="J688" t="n">
+        <v>2</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr"/>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N688" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V688" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Apartadó</t>
+        </is>
+      </c>
+      <c r="F689" t="n">
+        <v>119055</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO LABORAL</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I689" t="n">
+        <v>26</v>
+      </c>
+      <c r="J689" t="n">
+        <v>2</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr"/>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N689" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V689" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>119086</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD CONTRACTUAL Y EXTRACONTRACTUAL DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I690" t="n">
+        <v>26</v>
+      </c>
+      <c r="J690" t="n">
+        <v>2</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr"/>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Bimensual</t>
+        </is>
+      </c>
+      <c r="N690" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V690" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE INVESTIGACION Y DESARROLLO - UDI</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F691" t="n">
+        <v>119163</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN  GESTIÓN TECNOLOGÍA E INNOVACIÓN</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I691" t="n">
+        <v>89</v>
+      </c>
+      <c r="J691" t="n">
+        <v>8</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr"/>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N691" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V691" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA ANTONIO JOSE DE SUCRE - CORPOSUCRE</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F692" t="n">
+        <v>119045</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I692" t="n">
+        <v>26</v>
+      </c>
+      <c r="J692" t="n">
+        <v>2</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr"/>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N692" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V692" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>3718</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>FUNDACION DE ESTUDIOS SUPERIORES COMFANORTE -F.E.S.C.-</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>San José de Cúcuta</t>
+        </is>
+      </c>
+      <c r="F693" t="n">
+        <v>119064</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I693" t="n">
+        <v>26</v>
+      </c>
+      <c r="J693" t="n">
+        <v>2</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr"/>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N693" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V693" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>CORPORACION TECNOLOGICA INDUSTRIAL COLOMBIANA - TEINCO</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F694" t="n">
+        <v>119079</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EFICIENCIA ENERGÉTICA Y DESARROLLO SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I694" t="n">
+        <v>24</v>
+      </c>
+      <c r="J694" t="n">
+        <v>2</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr"/>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N694" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V694" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>CORPORACION TECNOLOGICA INDUSTRIAL COLOMBIANA - TEINCO</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F695" t="n">
+        <v>119080</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EFICIENCIA ENERGÉTICA Y DESARROLLO SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I695" t="n">
+        <v>24</v>
+      </c>
+      <c r="J695" t="n">
+        <v>2</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr"/>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N695" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V695" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>3831</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA COMFACAUCA - UNICOMFACAUCA</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F696" t="n">
+        <v>118804</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GOBERNANZA Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I696" t="n">
+        <v>43</v>
+      </c>
+      <c r="J696" t="n">
+        <v>4</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr"/>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N696" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V696" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SAN MATEO - SAN MATEO EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F697" t="n">
+        <v>119090</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I697" t="n">
+        <v>28</v>
+      </c>
+      <c r="J697" t="n">
+        <v>2</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr"/>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N697" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V697" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SAN MATEO - SAN MATEO EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="n">
+        <v>119108</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN HIGIENE, SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I698" t="n">
+        <v>32</v>
+      </c>
+      <c r="J698" t="n">
+        <v>2</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr"/>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N698" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V698" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F699" t="n">
+        <v>119032</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y DESARROLLO DE VIDEOJUEGOS</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I699" t="n">
+        <v>28</v>
+      </c>
+      <c r="J699" t="n">
+        <v>2</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N699" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V699" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F700" t="n">
+        <v>119153</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN MARKETING POLÍTICO</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I700" t="n">
+        <v>28</v>
+      </c>
+      <c r="J700" t="n">
+        <v>2</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N700" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V700" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F701" t="n">
+        <v>119049</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I701" t="n">
+        <v>136</v>
+      </c>
+      <c r="J701" t="n">
+        <v>8</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N701" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V701" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F702" t="n">
+        <v>119047</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I702" t="n">
+        <v>136</v>
+      </c>
+      <c r="J702" t="n">
+        <v>8</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N702" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q702" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V702" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
+        <v>119048</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I703" t="n">
+        <v>136</v>
+      </c>
+      <c r="J703" t="n">
+        <v>8</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N703" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V703" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F704" t="n">
+        <v>119135</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I704" t="n">
+        <v>28</v>
+      </c>
+      <c r="J704" t="n">
+        <v>2</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N704" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V704" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F705" t="n">
+        <v>119134</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I705" t="n">
+        <v>28</v>
+      </c>
+      <c r="J705" t="n">
+        <v>2</v>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N705" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V705" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>119043</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I706" t="n">
+        <v>26</v>
+      </c>
+      <c r="J706" t="n">
+        <v>2</v>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N706" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T706" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V706" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F707" t="n">
+        <v>119042</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I707" t="n">
+        <v>26</v>
+      </c>
+      <c r="J707" t="n">
+        <v>2</v>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N707" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T707" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V707" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F708" t="n">
+        <v>119044</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I708" t="n">
+        <v>26</v>
+      </c>
+      <c r="J708" t="n">
+        <v>2</v>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr"/>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N708" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q708" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T708" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U708" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V708" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="n">
+        <v>119120</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I709" t="n">
+        <v>28</v>
+      </c>
+      <c r="J709" t="n">
+        <v>2</v>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr"/>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N709" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q709" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S709" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T709" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U709" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V709" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F710" t="n">
+        <v>119046</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I710" t="n">
+        <v>26</v>
+      </c>
+      <c r="J710" t="n">
+        <v>2</v>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr"/>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N710" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q710" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T710" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U710" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V710" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr"/>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="n">
+        <v>119118</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PÚBLICA TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I711" t="n">
+        <v>28</v>
+      </c>
+      <c r="J711" t="n">
+        <v>2</v>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr"/>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N711" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T711" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V711" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="n">
+        <v>119117</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PÚBLICA TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I712" t="n">
+        <v>28</v>
+      </c>
+      <c r="J712" t="n">
+        <v>2</v>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr"/>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N712" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q712" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T712" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V712" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr"/>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="n">
+        <v>119115</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD SOCIAL CORPORATIVA</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I713" t="n">
+        <v>25</v>
+      </c>
+      <c r="J713" t="n">
+        <v>2</v>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr"/>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N713" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T713" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V713" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="n">
+        <v>119116</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD SOCIAL CORPORATIVA</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I714" t="n">
+        <v>25</v>
+      </c>
+      <c r="J714" t="n">
+        <v>2</v>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N714" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T714" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V714" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>119035</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I715" t="n">
+        <v>47</v>
+      </c>
+      <c r="J715" t="n">
+        <v>3</v>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr"/>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N715" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q715" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T715" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V715" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA VIRTUAL INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F716" t="n">
+        <v>118878</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I716" t="n">
+        <v>26</v>
+      </c>
+      <c r="J716" t="n">
+        <v>4</v>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N716" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q716" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T716" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V716" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA VIRTUAL INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F717" t="n">
+        <v>118879</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I717" t="n">
+        <v>26</v>
+      </c>
+      <c r="J717" t="n">
+        <v>4</v>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr"/>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N717" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q717" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V717" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="n">
+        <v>119107</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIENCIAS PENALES</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I718" t="n">
+        <v>24</v>
+      </c>
+      <c r="J718" t="n">
+        <v>2</v>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr"/>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N718" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q718" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T718" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V718" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F719" t="n">
+        <v>119040</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO GRÁFICO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I719" t="n">
+        <v>24</v>
+      </c>
+      <c r="J719" t="n">
+        <v>2</v>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr"/>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N719" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>Artes plásticas, visuales y afines</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T719" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>Música</t>
         </is>
       </c>
     </row>
